--- a/Configs/GameConfig/Datas/roguelike_spawn_stage.xlsx
+++ b/Configs/GameConfig/Datas/roguelike_spawn_stage.xlsx
@@ -260,7 +260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3;2;1</t>
+          <t>4;2;1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -527,7 +527,7 @@
         <v>9999</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -535,19 +535,19 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>slime;bat;guard;wisp;mushroom_guard</t>
+          <t>slime;bat;wisp;mushroom_guard</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2;3;2;2;1</t>
+          <t>3;3;2;1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -556,14 +556,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>9999</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -571,44 +571,113 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>bat;guard;wisp;crystal_bug;mushroom_guard</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3;2;2;2;1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>moon_knight</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>210</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>9999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>360</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>bat;guard;crystal_bug;mushroom_guard</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2;2;3;1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2;2;3;2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>moon_knight</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>120</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H9" t="n">
+        <v>390</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>9999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>540</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>guard;crystal_bug;mushroom_guard;wisp</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2;3;2;1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>moon_knight</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>540</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>dungeon_heart</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>300</v>
-      </c>
-      <c r="K8" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+      <c r="J10" t="n">
+        <v>600</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
